--- a/WorkBot/refactor/data/orders/Webstaurant/Webstaurant_Bakery_2025-10-11.xlsx
+++ b/WorkBot/refactor/data/orders/Webstaurant/Webstaurant_Bakery_2025-10-11.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,6 +490,60 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>102.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>40862028</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hot Chocolate (Bulk)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>123.18</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>369.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>40862029</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>White Hot Chocolate - Ghirardelli</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>53.39</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>106.78</t>
         </is>
       </c>
     </row>

--- a/WorkBot/refactor/data/orders/Webstaurant/Webstaurant_Bakery_2025-10-11.xlsx
+++ b/WorkBot/refactor/data/orders/Webstaurant/Webstaurant_Bakery_2025-10-11.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,384 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>711SPRNKLEPK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sprinkles - Pink</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>23.79</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>47.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10207004</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Spice - Allspice</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>38.49</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>38.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10200118</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Spice - Crushed Red Pepper</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>21.99</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>10207579</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Salt - Sea Coarse</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>21.17</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>84.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>245885CB</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Box Cake - 8x8x5</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>34.81</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>139.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>245CBT26183</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Box Cake - Full Sheet (Lid)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>44.07</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>44.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>63204854</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Degreaser - for Panini Press (Dawn)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>47.04</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>94.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>433SLINERBL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sheet Pan Liner - Silicone Coated</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>76.99</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>384.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>500CTOUT160</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Java Box (160oz)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>95.99</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>191.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5000TOUT96</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Java Box (96oz)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>82.99</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>165.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>245CCGR2518</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cake Board - Full Sheet</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>56.99</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>113.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>245CCGR1914</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cake Board - 1/2 Sheet</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>37.99</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>75.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>245CCGR1410BL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cake Board - 1/4 Sheet</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>40.49</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>80.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>433qlinerbl</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sheet Pan Liner - White</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>46.99</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>187.96</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
